--- a/accountant-skill/data/output/Feb2025/trial_balance_Feb2025.xlsx
+++ b/accountant-skill/data/output/Feb2025/trial_balance_Feb2025.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dr: 0.00 | Cr: 0.00</t>
+          <t>Dr: 473,566,123.00 | Cr: 473,566,123.00</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr: 497,562,751.55 | Cr: 497,562,751.55</t>
+          <t>Dr: 971,128,874.55 | Cr: 971,128,874.55</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,9 @@
           <t>Inventory - Raw Material</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
+      <c r="C8" s="4" t="n">
+        <v>5605177</v>
+      </c>
       <c r="D8" s="4" t="n">
         <v>9965463.779999999</v>
       </c>
@@ -654,7 +656,7 @@
         <v>5605177.44</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4360286.339999999</v>
+        <v>9965463.34</v>
       </c>
     </row>
     <row r="9">
@@ -666,7 +668,9 @@
           <t>Inventory - Packaging</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
+      <c r="C9" s="4" t="n">
+        <v>7899300</v>
+      </c>
       <c r="D9" s="4" t="n">
         <v>22801950</v>
       </c>
@@ -674,7 +678,7 @@
         <v>7899300</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14902650</v>
+        <v>22801950</v>
       </c>
     </row>
     <row r="10">
@@ -686,7 +690,9 @@
           <t>Inventory - Finished Goods</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="4" t="n">
+        <v>34461646</v>
+      </c>
       <c r="D10" s="4" t="n">
         <v>50973912.77</v>
       </c>
@@ -694,7 +700,7 @@
         <v>34461646</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>16512266.77</v>
+        <v>50973912.77000001</v>
       </c>
     </row>
     <row r="11">
@@ -762,13 +768,15 @@
           <t xml:space="preserve">Land </t>
         </is>
       </c>
-      <c r="C15" s="4" t="n"/>
+      <c r="C15" s="4" t="n">
+        <v>219000000</v>
+      </c>
       <c r="D15" s="4" t="n">
         <v>210290000</v>
       </c>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
     </row>
     <row r="16">
@@ -780,10 +788,14 @@
           <t>Buildings &amp; Structures</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="n">
+        <v>133000000</v>
+      </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>133000000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -794,13 +806,15 @@
           <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="4" t="n">
+        <v>19950000</v>
+      </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n">
         <v>554166.67</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>554166.67</v>
+        <v>20504166.67</v>
       </c>
     </row>
     <row r="18">
@@ -812,10 +826,14 @@
           <t>Machinery &amp; Equipment</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="4" t="n">
+        <v>66400000</v>
+      </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="F18" s="4" t="n">
+        <v>66400000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -826,13 +844,15 @@
           <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
+      <c r="C19" s="4" t="n">
+        <v>12375300</v>
+      </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n">
         <v>343758.33</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>343758.33</v>
+        <v>12719058.33</v>
       </c>
     </row>
     <row r="20">
@@ -872,13 +892,15 @@
           <t>Electrical &amp; Utility Systems</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n"/>
+      <c r="C22" s="4" t="n">
+        <v>7200000</v>
+      </c>
       <c r="D22" s="4" t="n">
         <v>6856000</v>
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>6856000</v>
+        <v>14056000</v>
       </c>
     </row>
     <row r="23">
@@ -890,13 +912,15 @@
           <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
+      <c r="C23" s="4" t="n">
+        <v>1710000</v>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n">
         <v>47500</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>47500</v>
+        <v>1757500</v>
       </c>
     </row>
     <row r="24">
@@ -1038,13 +1062,15 @@
           <t>Paid-up Capital</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
+      <c r="C33" s="4" t="n">
+        <v>439530823</v>
+      </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n">
         <v>400000000</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>400000000</v>
+        <v>839530823</v>
       </c>
     </row>
     <row r="34">
@@ -1549,7 +1575,7 @@
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>0</v>
+        <v>473566123</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>900155454.99</v>
@@ -1558,7 +1584,7 @@
         <v>900155454.99</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>497562751.55</v>
+        <v>971128874.5500001</v>
       </c>
     </row>
   </sheetData>
